--- a/data/Gruzovie_ind_09-2025.xlsx
+++ b/data/Gruzovie_ind_09-2025.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Образование\Магистратура\Диплом\ITMO_NIR\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D9E9FB-9F90-43CE-B8CB-4629E2FA79E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="75" windowWidth="11790" windowHeight="9990" tabRatio="756"/>
+    <workbookView xWindow="6840" yWindow="8475" windowWidth="21600" windowHeight="11040" tabRatio="756" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Содержание" sheetId="9" r:id="rId1"/>
@@ -41,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="87">
   <si>
     <t>Транспорт - все виды</t>
   </si>
@@ -444,7 +450,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -1205,15 +1211,18 @@
   <cellStyles count="5">
     <cellStyle name="Гиперссылка" xfId="4" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 3" xfId="2"/>
-    <cellStyle name="Обычный 5" xfId="1"/>
-    <cellStyle name="Обычный_Лист1" xfId="3"/>
+    <cellStyle name="Обычный 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 5" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный_Лист1" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1238,6 +1247,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1283,6 +1297,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000003000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1328,6 +1347,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000003000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1373,6 +1397,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000003000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1418,6 +1447,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1463,6 +1497,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1508,6 +1547,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1553,6 +1597,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1598,6 +1647,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1643,6 +1697,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1688,6 +1747,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1733,6 +1797,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1778,6 +1847,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1823,6 +1897,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1868,6 +1947,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1913,6 +1997,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1700-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -1958,6 +2047,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1800-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -2003,6 +2097,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -2048,6 +2147,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -2091,7 +2195,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2131,6 +2241,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Рисунок 5">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000006000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -2174,7 +2289,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2214,6 +2335,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -2257,7 +2383,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2297,6 +2429,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -2340,7 +2477,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2380,6 +2523,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000003000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -2425,6 +2573,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000003000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -2494,7 +2647,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2527,9 +2680,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2562,6 +2732,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2737,7 +2924,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T43"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3768,31 +3955,31 @@
     <mergeCell ref="A43:D43"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A3:J3" location="'1'!A1" display="1. Индексы тарифов на грузовые перевозки по Российской Федерации в 2010-2020 гг."/>
-    <hyperlink ref="A4:M4" location="'2'!A1" display="2. Индексы тарифов на перевозку грузов железнодорожным транспортом по Российской Федерации в 2010-2020 гг."/>
-    <hyperlink ref="A5:M5" location="'3'!A1" display="3. Индексы тарифов на перевозку грузов автомобильным транспортом  по Российской Федерации в 2010-2020 гг."/>
-    <hyperlink ref="A6:O6" location="'4'!A1" display="4. Индексы тарифов на транспортировку (перекачку) грузов трубопроводным транспортом по Российской Федерации в 2010-2020 гг."/>
-    <hyperlink ref="A9:M9" location="'5'!A1" display="5. Индексы тарифов на грузовые перевозки по Российской Федерации в 2021 г. (к предыдущему месяцу)"/>
-    <hyperlink ref="A10:P10" location="'6'!A1" display="6. Индексы тарифов на грузовые перевозки по Российской Федерации в 2021 г. (к декабрю предыдущего года)"/>
-    <hyperlink ref="A11:P11" location="'7'!A1" display="7. Индексы тарифов на грузовые перевозки по Российской Федерации в 2021 г. (к соответствующему месяцу предыдущего года)"/>
-    <hyperlink ref="A12:T12" location="'8'!A1" display="8. Индексы тарифов на грузовые перевозки по Российской Федерации в 2021 г. (за период с начала года к соответствующему периоду предыдущего года)"/>
-    <hyperlink ref="A15:M15" location="'9'!A1" display="9. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (к предыдущему месяцу)"/>
-    <hyperlink ref="A16:P16" location="'10'!A1" display="10. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (к декабрю предыдущего года)"/>
-    <hyperlink ref="A17:P17" location="'11'!A1" display="11. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (к соответствующему месяцу предыдущего года)"/>
-    <hyperlink ref="A18:T18" location="'12'!A1" display="12. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (за период с начала года к соответствующему периоду предыдущего года)"/>
-    <hyperlink ref="A22:P22" location="'14'!A1" display="14. Индексы тарифов на грузовые перевозки по Российской Федерации в 2023 г. (к декабрю предыдущего года)"/>
-    <hyperlink ref="A23:P23" location="'11'!A1" display="11. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (к соответствующему месяцу предыдущего года)"/>
-    <hyperlink ref="A24:T24" location="'16'!A1" display="16. Индексы тарифов на грузовые перевозки по Российской Федерации в 2023 г. (за период с начала года к соответствующему периоду предыдущего года)"/>
-    <hyperlink ref="A21:M21" location="'13'!A1" display="13. Индексы тарифов на грузовые перевозки по Российской Федерации в 2023 г. (к предыдущему месяцу)"/>
-    <hyperlink ref="A23:T23" location="'15'!A1" display="15. Индексы тарифов на грузовые перевозки по Российской Федерации в 2023 г. (к соответствующему месяцу предыдущего года)"/>
-    <hyperlink ref="A27:M27" location="'17'!A1" display="17. Индексы тарифов на грузовые перевозки по Российской Федерации в 2024 г. (к предыдущему месяцу)"/>
-    <hyperlink ref="A28:P28" location="'18'!A1" display="18. Индексы тарифов на грузовые перевозки по Российской Федерации в 2024 г. (к декабрю предыдущего года)"/>
-    <hyperlink ref="A29:T29" location="'19'!A1" display="19. Индексы тарифов на грузовые перевозки по Российской Федерации в 2024 г. (к соответствующему месяцу предыдущего года)"/>
-    <hyperlink ref="A30:T30" location="'20'!A1" display="20. Индексы тарифов на грузовые перевозки по Российской Федерации в 2024 г. (за период с начала года к соответствующему периоду предыдущего года)"/>
-    <hyperlink ref="A33" location="'21'!A1" display="'21'!A1"/>
-    <hyperlink ref="A34:K34" location="'22'!A1" display="'22'!A1"/>
-    <hyperlink ref="A35:K35" location="'23'!A1" display="'23'!A1"/>
-    <hyperlink ref="A36:K36" location="'24'!A1" display="'24'!A1"/>
+    <hyperlink ref="A3:J3" location="'1'!A1" display="1. Индексы тарифов на грузовые перевозки по Российской Федерации в 2010-2020 гг." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A4:M4" location="'2'!A1" display="2. Индексы тарифов на перевозку грузов железнодорожным транспортом по Российской Федерации в 2010-2020 гг." xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A5:M5" location="'3'!A1" display="3. Индексы тарифов на перевозку грузов автомобильным транспортом  по Российской Федерации в 2010-2020 гг." xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A6:O6" location="'4'!A1" display="4. Индексы тарифов на транспортировку (перекачку) грузов трубопроводным транспортом по Российской Федерации в 2010-2020 гг." xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A9:M9" location="'5'!A1" display="5. Индексы тарифов на грузовые перевозки по Российской Федерации в 2021 г. (к предыдущему месяцу)" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A10:P10" location="'6'!A1" display="6. Индексы тарифов на грузовые перевозки по Российской Федерации в 2021 г. (к декабрю предыдущего года)" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="A11:P11" location="'7'!A1" display="7. Индексы тарифов на грузовые перевозки по Российской Федерации в 2021 г. (к соответствующему месяцу предыдущего года)" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="A12:T12" location="'8'!A1" display="8. Индексы тарифов на грузовые перевозки по Российской Федерации в 2021 г. (за период с начала года к соответствующему периоду предыдущего года)" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A15:M15" location="'9'!A1" display="9. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (к предыдущему месяцу)" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="A16:P16" location="'10'!A1" display="10. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (к декабрю предыдущего года)" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="A17:P17" location="'11'!A1" display="11. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (к соответствующему месяцу предыдущего года)" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A18:T18" location="'12'!A1" display="12. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (за период с начала года к соответствующему периоду предыдущего года)" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A22:P22" location="'14'!A1" display="14. Индексы тарифов на грузовые перевозки по Российской Федерации в 2023 г. (к декабрю предыдущего года)" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="A23:P23" location="'11'!A1" display="11. Индексы тарифов на грузовые перевозки по Российской Федерации в 2022 г. (к соответствующему месяцу предыдущего года)" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="A24:T24" location="'16'!A1" display="16. Индексы тарифов на грузовые перевозки по Российской Федерации в 2023 г. (за период с начала года к соответствующему периоду предыдущего года)" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A21:M21" location="'13'!A1" display="13. Индексы тарифов на грузовые перевозки по Российской Федерации в 2023 г. (к предыдущему месяцу)" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A23:T23" location="'15'!A1" display="15. Индексы тарифов на грузовые перевозки по Российской Федерации в 2023 г. (к соответствующему месяцу предыдущего года)" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="A27:M27" location="'17'!A1" display="17. Индексы тарифов на грузовые перевозки по Российской Федерации в 2024 г. (к предыдущему месяцу)" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="A28:P28" location="'18'!A1" display="18. Индексы тарифов на грузовые перевозки по Российской Федерации в 2024 г. (к декабрю предыдущего года)" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="A29:T29" location="'19'!A1" display="19. Индексы тарифов на грузовые перевозки по Российской Федерации в 2024 г. (к соответствующему месяцу предыдущего года)" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="A30:T30" location="'20'!A1" display="20. Индексы тарифов на грузовые перевозки по Российской Федерации в 2024 г. (за период с начала года к соответствующему периоду предыдущего года)" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A33" location="'21'!A1" display="'21'!A1" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="A34:K34" location="'22'!A1" display="'22'!A1" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="A35:K35" location="'23'!A1" display="'23'!A1" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="A36:K36" location="'24'!A1" display="'24'!A1" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.24" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="66" orientation="portrait" r:id="rId1"/>
@@ -3800,7 +3987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
@@ -4249,7 +4436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
@@ -4699,7 +4886,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
@@ -5149,7 +5336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
@@ -5594,7 +5781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
@@ -6044,7 +6231,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
@@ -6492,7 +6679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
@@ -6940,7 +7127,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
@@ -7390,7 +7577,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
@@ -7850,7 +8037,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
@@ -8295,7 +8482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:P20"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8696,14 +8883,14 @@
       <c r="M4" s="39">
         <v>2021</v>
       </c>
-      <c r="N4" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="O4" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="P4" s="39" t="s">
-        <v>78</v>
+      <c r="N4" s="39">
+        <v>2022</v>
+      </c>
+      <c r="O4" s="39">
+        <v>2023</v>
+      </c>
+      <c r="P4" s="39">
+        <v>2024</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9413,7 +9600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
@@ -9858,7 +10045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
@@ -10303,7 +10490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
@@ -10670,7 +10857,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
@@ -11031,7 +11218,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
@@ -11386,7 +11573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
@@ -11741,7 +11928,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12912,7 +13099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14084,7 +14271,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15255,7 +15442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -15713,7 +15900,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -16171,7 +16358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
@@ -16630,7 +16817,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
